--- a/r4-core-151-gda-triple/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T14:14:36+00:00</t>
+    <t>2026-10-19T12:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-151-gda-triple/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-151-gda-triple/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T12:51:52+00:00</t>
+    <t>2026-10-19T13:41:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3589,10 +3589,10 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S17" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>201</v>
@@ -4611,10 +4611,10 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -5301,10 +5301,10 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>201</v>
@@ -6323,10 +6323,10 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>21</v>
@@ -7013,10 +7013,10 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>201</v>
@@ -8035,10 +8035,10 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>21</v>
@@ -8725,10 +8725,10 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>201</v>
@@ -9747,10 +9747,10 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>21</v>
